--- a/AtchisonRegime/Outputs/Aust/df_regCLI_Aust.xlsx
+++ b/AtchisonRegime/Outputs/Aust/df_regCLI_Aust.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H676"/>
+  <dimension ref="A1:H677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17745,22 +17745,22 @@
         <v>45443</v>
       </c>
       <c r="B666" t="n">
-        <v>99.42</v>
+        <v>99.40072000000001</v>
       </c>
       <c r="C666" t="n">
-        <v>99.28331666666668</v>
+        <v>99.27688999999999</v>
       </c>
       <c r="D666" t="n">
-        <v>99.86826000000001</v>
+        <v>99.86772444444445</v>
       </c>
       <c r="E666" t="n">
-        <v>0.8842508565171998</v>
+        <v>0.884535899332654</v>
       </c>
       <c r="F666" t="b">
         <v>1</v>
       </c>
       <c r="G666" t="n">
-        <v>0.1460332201527155</v>
+        <v>0.1241894196525952</v>
       </c>
       <c r="H666" t="b">
         <v>1</v>
@@ -17771,22 +17771,22 @@
         <v>45473</v>
       </c>
       <c r="B667" t="n">
-        <v>99.62</v>
+        <v>99.59672</v>
       </c>
       <c r="C667" t="n">
-        <v>99.44362333333333</v>
+        <v>99.42943666666667</v>
       </c>
       <c r="D667" t="n">
-        <v>99.81505166666666</v>
+        <v>99.81386944444445</v>
       </c>
       <c r="E667" t="n">
-        <v>0.8374537676160221</v>
+        <v>0.8378831594404753</v>
       </c>
       <c r="F667" t="b">
         <v>1</v>
       </c>
       <c r="G667" t="n">
-        <v>0.2388191536463469</v>
+        <v>0.2339228301603335</v>
       </c>
       <c r="H667" t="b">
         <v>1</v>
@@ -17797,22 +17797,22 @@
         <v>45504</v>
       </c>
       <c r="B668" t="n">
-        <v>99.81</v>
+        <v>99.78400999999999</v>
       </c>
       <c r="C668" t="n">
-        <v>99.61666666666667</v>
+        <v>99.59381666666667</v>
       </c>
       <c r="D668" t="n">
-        <v>99.76972388888889</v>
+        <v>99.76781972222221</v>
       </c>
       <c r="E668" t="n">
-        <v>0.7896881475413545</v>
+        <v>0.79004664481277</v>
       </c>
       <c r="F668" t="b">
         <v>1</v>
       </c>
       <c r="G668" t="n">
-        <v>0.2406013064670542</v>
+        <v>0.2370619522653315</v>
       </c>
       <c r="H668" t="b">
         <v>1</v>
@@ -17823,22 +17823,22 @@
         <v>45535</v>
       </c>
       <c r="B669" t="n">
-        <v>99.95999999999999</v>
+        <v>99.93259999999999</v>
       </c>
       <c r="C669" t="n">
-        <v>99.79666666666667</v>
+        <v>99.77110999999998</v>
       </c>
       <c r="D669" t="n">
-        <v>99.73311277777778</v>
+        <v>99.73044750000001</v>
       </c>
       <c r="E669" t="n">
-        <v>0.7471720530396555</v>
+        <v>0.7472293014879334</v>
       </c>
       <c r="F669" t="b">
         <v>1</v>
       </c>
       <c r="G669" t="n">
-        <v>0.2007569734303624</v>
+        <v>0.1988546216055985</v>
       </c>
       <c r="H669" t="b">
         <v>1</v>
@@ -17849,22 +17849,22 @@
         <v>45565</v>
       </c>
       <c r="B670" t="n">
-        <v>100.06</v>
+        <v>100.0343</v>
       </c>
       <c r="C670" t="n">
-        <v>99.94333333333333</v>
+        <v>99.91696999999999</v>
       </c>
       <c r="D670" t="n">
-        <v>99.70509055555556</v>
+        <v>99.7017113888889</v>
       </c>
       <c r="E670" t="n">
-        <v>0.7138194804248312</v>
+        <v>0.7134166972220141</v>
       </c>
       <c r="F670" t="b">
         <v>1</v>
       </c>
       <c r="G670" t="n">
-        <v>0.1400914415231331</v>
+        <v>0.1425534339131948</v>
       </c>
       <c r="H670" t="b">
         <v>1</v>
@@ -17875,22 +17875,22 @@
         <v>45596</v>
       </c>
       <c r="B671" t="n">
-        <v>100.12</v>
+        <v>100.095</v>
       </c>
       <c r="C671" t="n">
-        <v>100.0466666666667</v>
+        <v>100.0206333333334</v>
       </c>
       <c r="D671" t="n">
-        <v>99.68453222222223</v>
+        <v>99.68045861111111</v>
       </c>
       <c r="E671" t="n">
-        <v>0.6898597493077361</v>
+        <v>0.688897041708825</v>
       </c>
       <c r="F671" t="b">
         <v>1</v>
       </c>
       <c r="G671" t="n">
-        <v>0.08697420027797154</v>
+        <v>0.0881118604449648</v>
       </c>
       <c r="H671" t="b">
         <v>1</v>
@@ -17901,22 +17901,22 @@
         <v>45626</v>
       </c>
       <c r="B672" t="n">
-        <v>100.15</v>
+        <v>100.1289</v>
       </c>
       <c r="C672" t="n">
-        <v>100.11</v>
+        <v>100.0860666666667</v>
       </c>
       <c r="D672" t="n">
-        <v>99.66939888888889</v>
+        <v>99.66473916666666</v>
       </c>
       <c r="E672" t="n">
-        <v>0.6728298704375655</v>
+        <v>0.6713224748866018</v>
       </c>
       <c r="F672" t="b">
         <v>1</v>
       </c>
       <c r="G672" t="n">
-        <v>0.04458779450515634</v>
+        <v>0.05049734109636209</v>
       </c>
       <c r="H672" t="b">
         <v>1</v>
@@ -17927,22 +17927,22 @@
         <v>45657</v>
       </c>
       <c r="B673" t="n">
-        <v>100.17</v>
+        <v>100.1633</v>
       </c>
       <c r="C673" t="n">
-        <v>100.1466666666667</v>
+        <v>100.1290666666667</v>
       </c>
       <c r="D673" t="n">
-        <v>99.65773777777777</v>
+        <v>99.65289194444443</v>
       </c>
       <c r="E673" t="n">
-        <v>0.6599365584665339</v>
+        <v>0.6581653679295523</v>
       </c>
       <c r="F673" t="b">
         <v>1</v>
       </c>
       <c r="G673" t="n">
-        <v>0.03030594341745388</v>
+        <v>0.05226649969174183</v>
       </c>
       <c r="H673" t="b">
         <v>1</v>
@@ -17953,22 +17953,22 @@
         <v>45688</v>
       </c>
       <c r="B674" t="n">
-        <v>100.2</v>
+        <v>100.2066</v>
       </c>
       <c r="C674" t="n">
-        <v>100.1733333333333</v>
+        <v>100.1662666666667</v>
       </c>
       <c r="D674" t="n">
-        <v>99.64836</v>
+        <v>99.6436975</v>
       </c>
       <c r="E674" t="n">
-        <v>0.6493907912541833</v>
+        <v>0.6476815511626436</v>
       </c>
       <c r="F674" t="b">
         <v>1</v>
       </c>
       <c r="G674" t="n">
-        <v>0.04619714416039293</v>
+        <v>0.06685384186450997</v>
       </c>
       <c r="H674" t="b">
         <v>1</v>
@@ -17979,22 +17979,22 @@
         <v>45716</v>
       </c>
       <c r="B675" t="n">
-        <v>100.22</v>
+        <v>100.2561</v>
       </c>
       <c r="C675" t="n">
-        <v>100.1966666666667</v>
+        <v>100.2086666666667</v>
       </c>
       <c r="D675" t="n">
-        <v>99.63987944444445</v>
+        <v>99.63621972222222</v>
       </c>
       <c r="E675" t="n">
-        <v>0.6395300373642608</v>
+        <v>0.6387040348862232</v>
       </c>
       <c r="F675" t="b">
         <v>1</v>
       </c>
       <c r="G675" t="n">
-        <v>0.03127296425735279</v>
+        <v>0.0775006846619135</v>
       </c>
       <c r="H675" t="b">
         <v>1</v>
@@ -18005,24 +18005,50 @@
         <v>45747</v>
       </c>
       <c r="B676" t="n">
-        <v>100.25</v>
+        <v>100.3141</v>
       </c>
       <c r="C676" t="n">
-        <v>100.2233333333333</v>
+        <v>100.2589333333333</v>
       </c>
       <c r="D676" t="n">
-        <v>99.63172388888889</v>
+        <v>99.62984472222223</v>
       </c>
       <c r="E676" t="n">
-        <v>0.6294690547904273</v>
+        <v>0.6304809770846836</v>
       </c>
       <c r="F676" t="b">
         <v>1</v>
       </c>
       <c r="G676" t="n">
-        <v>0.04765921338260101</v>
+        <v>0.09199325928623918</v>
       </c>
       <c r="H676" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B677" t="n">
+        <v>100.3674</v>
+      </c>
+      <c r="C677" t="n">
+        <v>100.3125333333333</v>
+      </c>
+      <c r="D677" t="n">
+        <v>99.62408083333332</v>
+      </c>
+      <c r="E677" t="n">
+        <v>0.6224922601716388</v>
+      </c>
+      <c r="F677" t="b">
+        <v>1</v>
+      </c>
+      <c r="G677" t="n">
+        <v>0.08562355455682437</v>
+      </c>
+      <c r="H677" t="b">
         <v>1</v>
       </c>
     </row>

--- a/AtchisonRegime/Outputs/Aust/df_regCLI_Aust.xlsx
+++ b/AtchisonRegime/Outputs/Aust/df_regCLI_Aust.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H677"/>
+  <dimension ref="A1:H678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17771,22 +17771,22 @@
         <v>45473</v>
       </c>
       <c r="B667" t="n">
-        <v>99.59672</v>
+        <v>99.56477</v>
       </c>
       <c r="C667" t="n">
-        <v>99.42943666666667</v>
+        <v>99.41878666666666</v>
       </c>
       <c r="D667" t="n">
-        <v>99.81386944444445</v>
+        <v>99.81298194444445</v>
       </c>
       <c r="E667" t="n">
-        <v>0.8378831594404753</v>
+        <v>0.8381366221218415</v>
       </c>
       <c r="F667" t="b">
         <v>1</v>
       </c>
       <c r="G667" t="n">
-        <v>0.2339228301603335</v>
+        <v>0.1957318122965168</v>
       </c>
       <c r="H667" t="b">
         <v>1</v>
@@ -17797,22 +17797,22 @@
         <v>45504</v>
       </c>
       <c r="B668" t="n">
-        <v>99.78400999999999</v>
+        <v>99.74919</v>
       </c>
       <c r="C668" t="n">
-        <v>99.59381666666667</v>
+        <v>99.57156000000002</v>
       </c>
       <c r="D668" t="n">
-        <v>99.76781972222221</v>
+        <v>99.76596499999999</v>
       </c>
       <c r="E668" t="n">
-        <v>0.79004664481277</v>
+        <v>0.7902620670330979</v>
       </c>
       <c r="F668" t="b">
         <v>1</v>
       </c>
       <c r="G668" t="n">
-        <v>0.2370619522653315</v>
+        <v>0.2333656234980073</v>
       </c>
       <c r="H668" t="b">
         <v>1</v>
@@ -17823,22 +17823,22 @@
         <v>45535</v>
       </c>
       <c r="B669" t="n">
-        <v>99.93259999999999</v>
+        <v>99.89503999999999</v>
       </c>
       <c r="C669" t="n">
-        <v>99.77110999999998</v>
+        <v>99.73633333333332</v>
       </c>
       <c r="D669" t="n">
-        <v>99.73044750000001</v>
+        <v>99.72754944444445</v>
       </c>
       <c r="E669" t="n">
-        <v>0.7472293014879334</v>
+        <v>0.7470949078815513</v>
       </c>
       <c r="F669" t="b">
         <v>1</v>
       </c>
       <c r="G669" t="n">
-        <v>0.1988546216055985</v>
+        <v>0.1952228538320057</v>
       </c>
       <c r="H669" t="b">
         <v>1</v>
@@ -17849,22 +17849,22 @@
         <v>45565</v>
       </c>
       <c r="B670" t="n">
-        <v>100.0343</v>
+        <v>99.9945</v>
       </c>
       <c r="C670" t="n">
-        <v>99.91696999999999</v>
+        <v>99.87957666666667</v>
       </c>
       <c r="D670" t="n">
-        <v>99.7017113888889</v>
+        <v>99.69770777777778</v>
       </c>
       <c r="E670" t="n">
-        <v>0.7134166972220141</v>
+        <v>0.7126515616689667</v>
       </c>
       <c r="F670" t="b">
         <v>1</v>
       </c>
       <c r="G670" t="n">
-        <v>0.1425534339131948</v>
+        <v>0.1395632948127991</v>
       </c>
       <c r="H670" t="b">
         <v>1</v>
@@ -17875,22 +17875,22 @@
         <v>45596</v>
       </c>
       <c r="B671" t="n">
-        <v>100.095</v>
+        <v>100.0541</v>
       </c>
       <c r="C671" t="n">
-        <v>100.0206333333334</v>
+        <v>99.98121333333334</v>
       </c>
       <c r="D671" t="n">
-        <v>99.68045861111111</v>
+        <v>99.6753188888889</v>
       </c>
       <c r="E671" t="n">
-        <v>0.688897041708825</v>
+        <v>0.6872999550114536</v>
       </c>
       <c r="F671" t="b">
         <v>1</v>
       </c>
       <c r="G671" t="n">
-        <v>0.0881118604449648</v>
+        <v>0.08671614127926139</v>
       </c>
       <c r="H671" t="b">
         <v>1</v>
@@ -17901,22 +17901,22 @@
         <v>45626</v>
       </c>
       <c r="B672" t="n">
-        <v>100.1289</v>
+        <v>100.0893</v>
       </c>
       <c r="C672" t="n">
-        <v>100.0860666666667</v>
+        <v>100.0459666666667</v>
       </c>
       <c r="D672" t="n">
-        <v>99.66473916666666</v>
+        <v>99.65849944444443</v>
       </c>
       <c r="E672" t="n">
-        <v>0.6713224748866018</v>
+        <v>0.668798441479506</v>
       </c>
       <c r="F672" t="b">
         <v>1</v>
       </c>
       <c r="G672" t="n">
-        <v>0.05049734109636209</v>
+        <v>0.05263170159625388</v>
       </c>
       <c r="H672" t="b">
         <v>1</v>
@@ -17927,22 +17927,22 @@
         <v>45657</v>
       </c>
       <c r="B673" t="n">
-        <v>100.1633</v>
+        <v>100.1283</v>
       </c>
       <c r="C673" t="n">
-        <v>100.1290666666667</v>
+        <v>100.0905666666667</v>
       </c>
       <c r="D673" t="n">
-        <v>99.65289194444443</v>
+        <v>99.64568</v>
       </c>
       <c r="E673" t="n">
-        <v>0.6581653679295523</v>
+        <v>0.6547119999336849</v>
       </c>
       <c r="F673" t="b">
         <v>1</v>
       </c>
       <c r="G673" t="n">
-        <v>0.05226649969174183</v>
+        <v>0.05956817654778246</v>
       </c>
       <c r="H673" t="b">
         <v>1</v>
@@ -17953,22 +17953,22 @@
         <v>45688</v>
       </c>
       <c r="B674" t="n">
-        <v>100.2066</v>
+        <v>100.1812</v>
       </c>
       <c r="C674" t="n">
-        <v>100.1662666666667</v>
+        <v>100.1329333333333</v>
       </c>
       <c r="D674" t="n">
-        <v>99.6436975</v>
+        <v>99.63578000000001</v>
       </c>
       <c r="E674" t="n">
-        <v>0.6476815511626436</v>
+        <v>0.6434373123867262</v>
       </c>
       <c r="F674" t="b">
         <v>1</v>
       </c>
       <c r="G674" t="n">
-        <v>0.06685384186450997</v>
+        <v>0.08221469128637288</v>
       </c>
       <c r="H674" t="b">
         <v>1</v>
@@ -17979,22 +17979,22 @@
         <v>45716</v>
       </c>
       <c r="B675" t="n">
-        <v>100.2561</v>
+        <v>100.2467</v>
       </c>
       <c r="C675" t="n">
-        <v>100.2086666666667</v>
+        <v>100.1854</v>
       </c>
       <c r="D675" t="n">
-        <v>99.63621972222222</v>
+        <v>99.62804111111112</v>
       </c>
       <c r="E675" t="n">
-        <v>0.6387040348862232</v>
+        <v>0.6340398023909066</v>
       </c>
       <c r="F675" t="b">
         <v>1</v>
       </c>
       <c r="G675" t="n">
-        <v>0.0775006846619135</v>
+        <v>0.1033058173209403</v>
       </c>
       <c r="H675" t="b">
         <v>1</v>
@@ -18005,22 +18005,22 @@
         <v>45747</v>
       </c>
       <c r="B676" t="n">
-        <v>100.3141</v>
+        <v>100.3279</v>
       </c>
       <c r="C676" t="n">
-        <v>100.2589333333333</v>
+        <v>100.2519333333333</v>
       </c>
       <c r="D676" t="n">
-        <v>99.62984472222223</v>
+        <v>99.62204944444444</v>
       </c>
       <c r="E676" t="n">
-        <v>0.6304809770846836</v>
+        <v>0.6261101789938501</v>
       </c>
       <c r="F676" t="b">
         <v>1</v>
       </c>
       <c r="G676" t="n">
-        <v>0.09199325928623918</v>
+        <v>0.1296896340680529</v>
       </c>
       <c r="H676" t="b">
         <v>1</v>
@@ -18031,28 +18031,341 @@
         <v>45777</v>
       </c>
       <c r="B677" t="n">
-        <v>100.3674</v>
+        <v>100.4102</v>
       </c>
       <c r="C677" t="n">
-        <v>100.3125333333333</v>
+        <v>100.3282666666667</v>
       </c>
       <c r="D677" t="n">
-        <v>99.62408083333332</v>
+        <v>99.61747444444444</v>
       </c>
       <c r="E677" t="n">
-        <v>0.6224922601716388</v>
+        <v>0.6195157575048882</v>
       </c>
       <c r="F677" t="b">
         <v>1</v>
       </c>
       <c r="G677" t="n">
-        <v>0.08562355455682437</v>
+        <v>0.1328456927899113</v>
       </c>
       <c r="H677" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="2" t="n">
+        <v>45808</v>
+      </c>
+      <c r="B678" t="n">
+        <v>100.5006</v>
+      </c>
+      <c r="C678" t="n">
+        <v>100.4129</v>
+      </c>
+      <c r="D678" t="n">
+        <v>99.61492166666667</v>
+      </c>
+      <c r="E678" t="n">
+        <v>0.6155599865279717</v>
+      </c>
+      <c r="F678" t="b">
+        <v>1</v>
+      </c>
+      <c r="G678" t="n">
+        <v>0.1468581486426662</v>
+      </c>
+      <c r="H678" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005C6577D0C3AE724BBB504F46D5A19401" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="17afb16e0fbe716d3dcf2481b32b5550">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="df76e320-99cb-4a11-b59f-8bf32867ab70" xmlns:ns3="c0789f30-979e-497b-8344-faefb3987540" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f6d0bb8d4e6a5d6b988ea2ed2503dbb5" ns2:_="" ns3:_="">
+    <xsd:import namespace="df76e320-99cb-4a11-b59f-8bf32867ab70"/>
+    <xsd:import namespace="c0789f30-979e-497b-8344-faefb3987540"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="df76e320-99cb-4a11-b59f-8bf32867ab70" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="14" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="15" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="21" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2ea5f6a7-5373-4784-9cd5-4ca8be386d98" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="23" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c0789f30-979e-497b-8344-faefb3987540" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="22" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{f1100522-260f-4f17-9a31-47a12622b1e0}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="c0789f30-979e-497b-8344-faefb3987540">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c0789f30-979e-497b-8344-faefb3987540" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="df76e320-99cb-4a11-b59f-8bf32867ab70">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84C0C125-5D1E-4DD3-8EA0-B525FC34CA1A}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D825304F-AEEC-47FC-835B-443872433A1A}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1796A7A-A571-4E87-944D-572D6AF27443}"/>
 </file>
--- a/AtchisonRegime/Outputs/Aust/df_regCLI_Aust.xlsx
+++ b/AtchisonRegime/Outputs/Aust/df_regCLI_Aust.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H678"/>
+  <dimension ref="A1:H679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17797,22 +17797,22 @@
         <v>45504</v>
       </c>
       <c r="B668" t="n">
-        <v>99.74919</v>
+        <v>99.69</v>
       </c>
       <c r="C668" t="n">
-        <v>99.57156000000002</v>
+        <v>99.55183</v>
       </c>
       <c r="D668" t="n">
-        <v>99.76596499999999</v>
+        <v>99.76432083333333</v>
       </c>
       <c r="E668" t="n">
-        <v>0.7902620670330979</v>
+        <v>0.7903595325288878</v>
       </c>
       <c r="F668" t="b">
         <v>1</v>
       </c>
       <c r="G668" t="n">
-        <v>0.2333656234980073</v>
+        <v>0.1584468774600688</v>
       </c>
       <c r="H668" t="b">
         <v>1</v>
@@ -17823,22 +17823,22 @@
         <v>45535</v>
       </c>
       <c r="B669" t="n">
-        <v>99.89503999999999</v>
+        <v>99.83</v>
       </c>
       <c r="C669" t="n">
-        <v>99.73633333333332</v>
+        <v>99.69492333333334</v>
       </c>
       <c r="D669" t="n">
-        <v>99.72754944444445</v>
+        <v>99.72409861111112</v>
       </c>
       <c r="E669" t="n">
-        <v>0.7470949078815513</v>
+        <v>0.7467689263684245</v>
       </c>
       <c r="F669" t="b">
         <v>1</v>
       </c>
       <c r="G669" t="n">
-        <v>0.1952228538320057</v>
+        <v>0.1874743244618221</v>
       </c>
       <c r="H669" t="b">
         <v>1</v>
@@ -17849,22 +17849,22 @@
         <v>45565</v>
       </c>
       <c r="B670" t="n">
-        <v>99.9945</v>
+        <v>99.92</v>
       </c>
       <c r="C670" t="n">
-        <v>99.87957666666667</v>
+        <v>99.81333333333333</v>
       </c>
       <c r="D670" t="n">
-        <v>99.69770777777778</v>
+        <v>99.69218749999999</v>
       </c>
       <c r="E670" t="n">
-        <v>0.7126515616689667</v>
+        <v>0.7113715138092738</v>
       </c>
       <c r="F670" t="b">
         <v>1</v>
       </c>
       <c r="G670" t="n">
-        <v>0.1395632948127991</v>
+        <v>0.1265161708796416</v>
       </c>
       <c r="H670" t="b">
         <v>1</v>
@@ -17875,22 +17875,22 @@
         <v>45596</v>
       </c>
       <c r="B671" t="n">
-        <v>100.0541</v>
+        <v>99.98</v>
       </c>
       <c r="C671" t="n">
-        <v>99.98121333333334</v>
+        <v>99.91000000000001</v>
       </c>
       <c r="D671" t="n">
-        <v>99.6753188888889</v>
+        <v>99.66774027777778</v>
       </c>
       <c r="E671" t="n">
-        <v>0.6872999550114536</v>
+        <v>0.6847112112895861</v>
       </c>
       <c r="F671" t="b">
         <v>1</v>
       </c>
       <c r="G671" t="n">
-        <v>0.08671614127926139</v>
+        <v>0.08762818398576852</v>
       </c>
       <c r="H671" t="b">
         <v>1</v>
@@ -17901,22 +17901,22 @@
         <v>45626</v>
       </c>
       <c r="B672" t="n">
-        <v>100.0893</v>
+        <v>100.02</v>
       </c>
       <c r="C672" t="n">
-        <v>100.0459666666667</v>
+        <v>99.97333333333334</v>
       </c>
       <c r="D672" t="n">
-        <v>99.65849944444443</v>
+        <v>99.64899583333333</v>
       </c>
       <c r="E672" t="n">
-        <v>0.668798441479506</v>
+        <v>0.6647366178328665</v>
       </c>
       <c r="F672" t="b">
         <v>1</v>
       </c>
       <c r="G672" t="n">
-        <v>0.05263170159625388</v>
+        <v>0.06017420874209937</v>
       </c>
       <c r="H672" t="b">
         <v>1</v>
@@ -17927,22 +17927,22 @@
         <v>45657</v>
       </c>
       <c r="B673" t="n">
-        <v>100.1283</v>
+        <v>100.05</v>
       </c>
       <c r="C673" t="n">
-        <v>100.0905666666667</v>
+        <v>100.0166666666667</v>
       </c>
       <c r="D673" t="n">
-        <v>99.64568</v>
+        <v>99.63400138888888</v>
       </c>
       <c r="E673" t="n">
-        <v>0.6547119999336849</v>
+        <v>0.648805822781503</v>
       </c>
       <c r="F673" t="b">
         <v>1</v>
       </c>
       <c r="G673" t="n">
-        <v>0.05956817654778246</v>
+        <v>0.0462387958717568</v>
       </c>
       <c r="H673" t="b">
         <v>1</v>
@@ -17953,22 +17953,22 @@
         <v>45688</v>
       </c>
       <c r="B674" t="n">
-        <v>100.1812</v>
+        <v>100.08</v>
       </c>
       <c r="C674" t="n">
-        <v>100.1329333333333</v>
+        <v>100.05</v>
       </c>
       <c r="D674" t="n">
-        <v>99.63578000000001</v>
+        <v>99.62129027777777</v>
       </c>
       <c r="E674" t="n">
-        <v>0.6434373123867262</v>
+        <v>0.6349313248645349</v>
       </c>
       <c r="F674" t="b">
         <v>1</v>
       </c>
       <c r="G674" t="n">
-        <v>0.08221469128637288</v>
+        <v>0.04724920448113307</v>
       </c>
       <c r="H674" t="b">
         <v>1</v>
@@ -17979,22 +17979,22 @@
         <v>45716</v>
       </c>
       <c r="B675" t="n">
-        <v>100.2467</v>
+        <v>100.11</v>
       </c>
       <c r="C675" t="n">
-        <v>100.1854</v>
+        <v>100.08</v>
       </c>
       <c r="D675" t="n">
-        <v>99.62804111111112</v>
+        <v>99.60975416666666</v>
       </c>
       <c r="E675" t="n">
-        <v>0.6340398023909066</v>
+        <v>0.6216713698473547</v>
       </c>
       <c r="F675" t="b">
         <v>1</v>
       </c>
       <c r="G675" t="n">
-        <v>0.1033058173209403</v>
+        <v>0.04825700756875347</v>
       </c>
       <c r="H675" t="b">
         <v>1</v>
@@ -18005,22 +18005,22 @@
         <v>45747</v>
       </c>
       <c r="B676" t="n">
-        <v>100.3279</v>
+        <v>100.14</v>
       </c>
       <c r="C676" t="n">
-        <v>100.2519333333333</v>
+        <v>100.11</v>
       </c>
       <c r="D676" t="n">
-        <v>99.62204944444444</v>
+        <v>99.59854305555555</v>
       </c>
       <c r="E676" t="n">
-        <v>0.6261101789938501</v>
+        <v>0.6078346349828332</v>
       </c>
       <c r="F676" t="b">
         <v>1</v>
       </c>
       <c r="G676" t="n">
-        <v>0.1296896340680529</v>
+        <v>0.04935552907551643</v>
       </c>
       <c r="H676" t="b">
         <v>1</v>
@@ -18031,22 +18031,22 @@
         <v>45777</v>
       </c>
       <c r="B677" t="n">
-        <v>100.4102</v>
+        <v>100.19</v>
       </c>
       <c r="C677" t="n">
-        <v>100.3282666666667</v>
+        <v>100.1466666666667</v>
       </c>
       <c r="D677" t="n">
-        <v>99.61747444444444</v>
+        <v>99.58785138888888</v>
       </c>
       <c r="E677" t="n">
-        <v>0.6195157575048882</v>
+        <v>0.5933834278015171</v>
       </c>
       <c r="F677" t="b">
         <v>1</v>
       </c>
       <c r="G677" t="n">
-        <v>0.1328456927899113</v>
+        <v>0.08426254872881592</v>
       </c>
       <c r="H677" t="b">
         <v>1</v>
@@ -18057,24 +18057,50 @@
         <v>45808</v>
       </c>
       <c r="B678" t="n">
-        <v>100.5006</v>
+        <v>100.25</v>
       </c>
       <c r="C678" t="n">
-        <v>100.4129</v>
+        <v>100.1933333333333</v>
       </c>
       <c r="D678" t="n">
-        <v>99.61492166666667</v>
+        <v>99.5783375</v>
       </c>
       <c r="E678" t="n">
-        <v>0.6155599865279717</v>
+        <v>0.5793962295374195</v>
       </c>
       <c r="F678" t="b">
         <v>1</v>
       </c>
       <c r="G678" t="n">
-        <v>0.1468581486426662</v>
+        <v>0.1035560760343665</v>
       </c>
       <c r="H678" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="2" t="n">
+        <v>45838</v>
+      </c>
+      <c r="B679" t="n">
+        <v>100.33</v>
+      </c>
+      <c r="C679" t="n">
+        <v>100.2566666666667</v>
+      </c>
+      <c r="D679" t="n">
+        <v>99.57139583333333</v>
+      </c>
+      <c r="E679" t="n">
+        <v>0.5684473597459838</v>
+      </c>
+      <c r="F679" t="b">
+        <v>1</v>
+      </c>
+      <c r="G679" t="n">
+        <v>0.1407342274150892</v>
+      </c>
+      <c r="H679" t="b">
         <v>1</v>
       </c>
     </row>
@@ -18359,13 +18385,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84C0C125-5D1E-4DD3-8EA0-B525FC34CA1A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CFA7E57-D3EB-415E-9E68-083B40765C28}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D825304F-AEEC-47FC-835B-443872433A1A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB6CA3D4-95F0-44FD-B1DB-4B30898E6545}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1796A7A-A571-4E87-944D-572D6AF27443}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F1FFB45-E838-4A66-8958-1418980AEC02}"/>
 </file>
--- a/AtchisonRegime/Outputs/Aust/df_regCLI_Aust.xlsx
+++ b/AtchisonRegime/Outputs/Aust/df_regCLI_Aust.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H679"/>
+  <dimension ref="A1:H682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17823,22 +17823,22 @@
         <v>45535</v>
       </c>
       <c r="B669" t="n">
-        <v>99.83</v>
+        <v>99.80953</v>
       </c>
       <c r="C669" t="n">
-        <v>99.69492333333334</v>
+        <v>99.68810000000001</v>
       </c>
       <c r="D669" t="n">
-        <v>99.72409861111112</v>
+        <v>99.72353000000001</v>
       </c>
       <c r="E669" t="n">
-        <v>0.7467689263684245</v>
+        <v>0.7466937755810166</v>
       </c>
       <c r="F669" t="b">
         <v>1</v>
       </c>
       <c r="G669" t="n">
-        <v>0.1874743244618221</v>
+        <v>0.1600790095069279</v>
       </c>
       <c r="H669" t="b">
         <v>1</v>
@@ -17849,22 +17849,22 @@
         <v>45565</v>
       </c>
       <c r="B670" t="n">
-        <v>99.92</v>
+        <v>99.93568</v>
       </c>
       <c r="C670" t="n">
-        <v>99.81333333333333</v>
+        <v>99.81173666666666</v>
       </c>
       <c r="D670" t="n">
-        <v>99.69218749999999</v>
+        <v>99.69205444444444</v>
       </c>
       <c r="E670" t="n">
-        <v>0.7113715138092738</v>
+        <v>0.7114150180207116</v>
       </c>
       <c r="F670" t="b">
         <v>1</v>
       </c>
       <c r="G670" t="n">
-        <v>0.1265161708796416</v>
+        <v>0.1773226552779029</v>
       </c>
       <c r="H670" t="b">
         <v>1</v>
@@ -17875,22 +17875,22 @@
         <v>45596</v>
       </c>
       <c r="B671" t="n">
-        <v>99.98</v>
+        <v>99.99481</v>
       </c>
       <c r="C671" t="n">
-        <v>99.91000000000001</v>
+        <v>99.91334000000001</v>
       </c>
       <c r="D671" t="n">
-        <v>99.66774027777778</v>
+        <v>99.66801861111111</v>
       </c>
       <c r="E671" t="n">
-        <v>0.6847112112895861</v>
+        <v>0.684948986956196</v>
       </c>
       <c r="F671" t="b">
         <v>1</v>
       </c>
       <c r="G671" t="n">
-        <v>0.08762818398576852</v>
+        <v>0.08632759683718989</v>
       </c>
       <c r="H671" t="b">
         <v>1</v>
@@ -17901,22 +17901,22 @@
         <v>45626</v>
       </c>
       <c r="B672" t="n">
-        <v>100.02</v>
+        <v>100.0343</v>
       </c>
       <c r="C672" t="n">
-        <v>99.97333333333334</v>
+        <v>99.98826333333334</v>
       </c>
       <c r="D672" t="n">
-        <v>99.64899583333333</v>
+        <v>99.64967138888889</v>
       </c>
       <c r="E672" t="n">
-        <v>0.6647366178328665</v>
+        <v>0.6652216109931508</v>
       </c>
       <c r="F672" t="b">
         <v>1</v>
       </c>
       <c r="G672" t="n">
-        <v>0.06017420874209937</v>
+        <v>0.05936367572461095</v>
       </c>
       <c r="H672" t="b">
         <v>1</v>
@@ -17927,22 +17927,22 @@
         <v>45657</v>
       </c>
       <c r="B673" t="n">
-        <v>100.05</v>
+        <v>100.0664</v>
       </c>
       <c r="C673" t="n">
-        <v>100.0166666666667</v>
+        <v>100.0318366666667</v>
       </c>
       <c r="D673" t="n">
-        <v>99.63400138888888</v>
+        <v>99.6351325</v>
       </c>
       <c r="E673" t="n">
-        <v>0.648805822781503</v>
+        <v>0.6496241547689788</v>
       </c>
       <c r="F673" t="b">
         <v>1</v>
       </c>
       <c r="G673" t="n">
-        <v>0.0462387958717568</v>
+        <v>0.0494131872473481</v>
       </c>
       <c r="H673" t="b">
         <v>1</v>
@@ -17953,22 +17953,22 @@
         <v>45688</v>
       </c>
       <c r="B674" t="n">
-        <v>100.08</v>
+        <v>100.0915</v>
       </c>
       <c r="C674" t="n">
-        <v>100.05</v>
+        <v>100.0640666666666</v>
       </c>
       <c r="D674" t="n">
-        <v>99.62129027777777</v>
+        <v>99.62274083333334</v>
       </c>
       <c r="E674" t="n">
-        <v>0.6349313248645349</v>
+        <v>0.6360300929555354</v>
       </c>
       <c r="F674" t="b">
         <v>1</v>
       </c>
       <c r="G674" t="n">
-        <v>0.04724920448113307</v>
+        <v>0.03946354154936113</v>
       </c>
       <c r="H674" t="b">
         <v>1</v>
@@ -17979,22 +17979,22 @@
         <v>45716</v>
       </c>
       <c r="B675" t="n">
-        <v>100.11</v>
+        <v>100.1063</v>
       </c>
       <c r="C675" t="n">
-        <v>100.08</v>
+        <v>100.0880666666667</v>
       </c>
       <c r="D675" t="n">
-        <v>99.60975416666666</v>
+        <v>99.61110194444444</v>
       </c>
       <c r="E675" t="n">
-        <v>0.6216713698473547</v>
+        <v>0.6227368050781948</v>
       </c>
       <c r="F675" t="b">
         <v>1</v>
       </c>
       <c r="G675" t="n">
-        <v>0.04825700756875347</v>
+        <v>0.02376605956050688</v>
       </c>
       <c r="H675" t="b">
         <v>1</v>
@@ -18005,22 +18005,22 @@
         <v>45747</v>
       </c>
       <c r="B676" t="n">
-        <v>100.14</v>
+        <v>100.1203</v>
       </c>
       <c r="C676" t="n">
-        <v>100.11</v>
+        <v>100.1060333333333</v>
       </c>
       <c r="D676" t="n">
-        <v>99.59854305555555</v>
+        <v>99.59934361111111</v>
       </c>
       <c r="E676" t="n">
-        <v>0.6078346349828332</v>
+        <v>0.6084592304133375</v>
       </c>
       <c r="F676" t="b">
         <v>1</v>
       </c>
       <c r="G676" t="n">
-        <v>0.04935552907551643</v>
+        <v>0.02300893683622046</v>
       </c>
       <c r="H676" t="b">
         <v>1</v>
@@ -18031,22 +18031,22 @@
         <v>45777</v>
       </c>
       <c r="B677" t="n">
-        <v>100.19</v>
+        <v>100.1385</v>
       </c>
       <c r="C677" t="n">
-        <v>100.1466666666667</v>
+        <v>100.1217</v>
       </c>
       <c r="D677" t="n">
-        <v>99.58785138888888</v>
+        <v>99.58722138888888</v>
       </c>
       <c r="E677" t="n">
-        <v>0.5933834278015171</v>
+        <v>0.5926087949212792</v>
       </c>
       <c r="F677" t="b">
         <v>1</v>
       </c>
       <c r="G677" t="n">
-        <v>0.08426254872881592</v>
+        <v>0.0307116602992886</v>
       </c>
       <c r="H677" t="b">
         <v>1</v>
@@ -18057,22 +18057,22 @@
         <v>45808</v>
       </c>
       <c r="B678" t="n">
-        <v>100.25</v>
+        <v>100.1695</v>
       </c>
       <c r="C678" t="n">
-        <v>100.1933333333333</v>
+        <v>100.1427666666667</v>
       </c>
       <c r="D678" t="n">
-        <v>99.5783375</v>
+        <v>99.57547138888889</v>
       </c>
       <c r="E678" t="n">
-        <v>0.5793962295374195</v>
+        <v>0.5760697993083793</v>
       </c>
       <c r="F678" t="b">
         <v>1</v>
       </c>
       <c r="G678" t="n">
-        <v>0.1035560760343665</v>
+        <v>0.05381292342911231</v>
       </c>
       <c r="H678" t="b">
         <v>1</v>
@@ -18083,24 +18083,102 @@
         <v>45838</v>
       </c>
       <c r="B679" t="n">
-        <v>100.33</v>
+        <v>100.2179</v>
       </c>
       <c r="C679" t="n">
-        <v>100.2566666666667</v>
+        <v>100.1753</v>
       </c>
       <c r="D679" t="n">
-        <v>99.57139583333333</v>
+        <v>99.56541583333333</v>
       </c>
       <c r="E679" t="n">
-        <v>0.5684473597459838</v>
+        <v>0.5609983970712116</v>
       </c>
       <c r="F679" t="b">
         <v>1</v>
       </c>
       <c r="G679" t="n">
-        <v>0.1407342274150892</v>
+        <v>0.0862747563142451</v>
       </c>
       <c r="H679" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="2" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B680" t="n">
+        <v>100.2731</v>
+      </c>
+      <c r="C680" t="n">
+        <v>100.2201666666667</v>
+      </c>
+      <c r="D680" t="n">
+        <v>99.55833805555555</v>
+      </c>
+      <c r="E680" t="n">
+        <v>0.5500080452389596</v>
+      </c>
+      <c r="F680" t="b">
+        <v>1</v>
+      </c>
+      <c r="G680" t="n">
+        <v>0.1003621682952233</v>
+      </c>
+      <c r="H680" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="2" t="n">
+        <v>45900</v>
+      </c>
+      <c r="B681" t="n">
+        <v>100.3164</v>
+      </c>
+      <c r="C681" t="n">
+        <v>100.2691333333333</v>
+      </c>
+      <c r="D681" t="n">
+        <v>99.55528805555555</v>
+      </c>
+      <c r="E681" t="n">
+        <v>0.5453425767603173</v>
+      </c>
+      <c r="F681" t="b">
+        <v>1</v>
+      </c>
+      <c r="G681" t="n">
+        <v>0.07939963216741985</v>
+      </c>
+      <c r="H681" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B682" t="n">
+        <v>100.3656</v>
+      </c>
+      <c r="C682" t="n">
+        <v>100.3183666666667</v>
+      </c>
+      <c r="D682" t="n">
+        <v>99.55828527777777</v>
+      </c>
+      <c r="E682" t="n">
+        <v>0.5495933020567819</v>
+      </c>
+      <c r="F682" t="b">
+        <v>1</v>
+      </c>
+      <c r="G682" t="n">
+        <v>0.08952074163908909</v>
+      </c>
+      <c r="H682" t="b">
         <v>1</v>
       </c>
     </row>
@@ -18385,13 +18463,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CFA7E57-D3EB-415E-9E68-083B40765C28}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FDE273D-216E-4A80-8318-12C7FDDF0ADE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB6CA3D4-95F0-44FD-B1DB-4B30898E6545}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E05BE203-86F6-4CA6-A3F0-1A1D425C6CE3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F1FFB45-E838-4A66-8958-1418980AEC02}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74BC9DE6-F927-4F66-BAD9-8662ED2EF3EC}"/>
 </file>